--- a/artfynd/A 47654-2023 artfynd.xlsx
+++ b/artfynd/A 47654-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113680638</v>
       </c>
       <c r="B2" t="n">
-        <v>91404</v>
+        <v>91406</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>113680504</v>
       </c>
       <c r="B3" t="n">
-        <v>91400</v>
+        <v>91402</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 47654-2023 artfynd.xlsx
+++ b/artfynd/A 47654-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113680638</v>
+        <v>113680504</v>
       </c>
       <c r="B2" t="n">
-        <v>91406</v>
+        <v>91402</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2059</v>
+        <v>4366</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>668914</v>
+        <v>668902</v>
       </c>
       <c r="R2" t="n">
-        <v>7076998</v>
+        <v>7076944</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-08-29</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-08-29</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,7 +765,7 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>Kristofer Wester</t>
+          <t>Tomas Rask</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Helene Andersson, Kristofer Wester</t>
+          <t>Helene Andersson, Tomas Rask</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113680504</v>
+        <v>113680638</v>
       </c>
       <c r="B3" t="n">
-        <v>91402</v>
+        <v>91406</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4366</v>
+        <v>2059</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>668902</v>
+        <v>668914</v>
       </c>
       <c r="R3" t="n">
-        <v>7076944</v>
+        <v>7076998</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -856,12 +856,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2023-08-29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2023-08-29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -876,7 +876,7 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>Tomas Rask</t>
+          <t>Kristofer Wester</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Helene Andersson, Tomas Rask</t>
+          <t>Helene Andersson, Kristofer Wester</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 47654-2023 artfynd.xlsx
+++ b/artfynd/A 47654-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113680504</v>
+        <v>113680638</v>
       </c>
       <c r="B2" t="n">
-        <v>91402</v>
+        <v>91410</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4366</v>
+        <v>2059</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>668902</v>
+        <v>668914</v>
       </c>
       <c r="R2" t="n">
-        <v>7076944</v>
+        <v>7076998</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2023-08-29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2023-08-29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,7 +765,7 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>Tomas Rask</t>
+          <t>Kristofer Wester</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Helene Andersson, Tomas Rask</t>
+          <t>Helene Andersson, Kristofer Wester</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113680638</v>
+        <v>113680504</v>
       </c>
       <c r="B3" t="n">
         <v>91406</v>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2059</v>
+        <v>4366</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>668914</v>
+        <v>668902</v>
       </c>
       <c r="R3" t="n">
-        <v>7076998</v>
+        <v>7076944</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -856,12 +856,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-08-29</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-08-29</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -876,7 +876,7 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>Kristofer Wester</t>
+          <t>Tomas Rask</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Helene Andersson, Kristofer Wester</t>
+          <t>Helene Andersson, Tomas Rask</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 47654-2023 artfynd.xlsx
+++ b/artfynd/A 47654-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113680638</v>
+        <v>113680504</v>
       </c>
       <c r="B2" t="n">
-        <v>91410</v>
+        <v>91406</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2059</v>
+        <v>4366</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>668914</v>
+        <v>668902</v>
       </c>
       <c r="R2" t="n">
-        <v>7076998</v>
+        <v>7076944</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-08-29</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-08-29</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,7 +765,7 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>Kristofer Wester</t>
+          <t>Tomas Rask</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Helene Andersson, Kristofer Wester</t>
+          <t>Helene Andersson, Tomas Rask</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113680504</v>
+        <v>113680638</v>
       </c>
       <c r="B3" t="n">
-        <v>91406</v>
+        <v>91410</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4366</v>
+        <v>2059</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>668902</v>
+        <v>668914</v>
       </c>
       <c r="R3" t="n">
-        <v>7076944</v>
+        <v>7076998</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -856,12 +856,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2023-08-29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2023-08-29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -876,7 +876,7 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>Tomas Rask</t>
+          <t>Kristofer Wester</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Helene Andersson, Tomas Rask</t>
+          <t>Helene Andersson, Kristofer Wester</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 47654-2023 artfynd.xlsx
+++ b/artfynd/A 47654-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113680504</v>
+        <v>113680638</v>
       </c>
       <c r="B2" t="n">
-        <v>91406</v>
+        <v>91410</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4366</v>
+        <v>2059</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>668902</v>
+        <v>668914</v>
       </c>
       <c r="R2" t="n">
-        <v>7076944</v>
+        <v>7076998</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2023-08-29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2023-08-29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,7 +765,7 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>Tomas Rask</t>
+          <t>Kristofer Wester</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Helene Andersson, Tomas Rask</t>
+          <t>Helene Andersson, Kristofer Wester</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113680638</v>
+        <v>113680504</v>
       </c>
       <c r="B3" t="n">
-        <v>91410</v>
+        <v>91406</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2059</v>
+        <v>4366</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>668914</v>
+        <v>668902</v>
       </c>
       <c r="R3" t="n">
-        <v>7076998</v>
+        <v>7076944</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -856,12 +856,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-08-29</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-08-29</t>
+          <t>2023-09-13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -876,7 +876,7 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>Kristofer Wester</t>
+          <t>Tomas Rask</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Helene Andersson, Kristofer Wester</t>
+          <t>Helene Andersson, Tomas Rask</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 47654-2023 artfynd.xlsx
+++ b/artfynd/A 47654-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
